--- a/Device_Config_2D.xlsx
+++ b/Device_Config_2D.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFBB17A-B336-4861-B2EA-27E4A9A295D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2620" yWindow="2620" windowWidth="28800" windowHeight="15370" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="28800" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AFQH" sheetId="50" r:id="rId1"/>
